--- a/2 курс/3 семестр/СиАОД/практика6_2.xlsx
+++ b/2 курс/3 семестр/СиАОД/практика6_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\1 курс\СИАОД\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\университет\СИАОД\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBED192-14C6-41DB-A8DB-B8E13E0D66CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FBC27F-4D3B-46A4-8DB7-5BCF009A0109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14325" xr2:uid="{9F89961C-6018-49CB-9608-3569904852F8}"/>
   </bookViews>
@@ -728,45 +728,45 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$A$10:$A$21</c:f>
+              <c:f>Лист1!$B$10:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>100000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>100000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>100000</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>100000</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>100000</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>100000</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>100000</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>100000</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
